--- a/sample.xlsx
+++ b/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\Project_Parallel_Selenium_Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1B5934-C0C0-4F4A-9B3D-E6C12A9AA02A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37CBC02-58DB-4F9D-90CD-F70A7543272F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
